--- a/artfynd/A 12228-2024 artfynd.xlsx
+++ b/artfynd/A 12228-2024 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>117466887</v>
       </c>
       <c r="B4" t="n">
-        <v>102747</v>
+        <v>102749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>117502973</v>
       </c>
       <c r="B5" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>117843332</v>
       </c>
       <c r="B6" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 12228-2024 artfynd.xlsx
+++ b/artfynd/A 12228-2024 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>121210372</v>
       </c>
       <c r="B7" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 12228-2024 artfynd.xlsx
+++ b/artfynd/A 12228-2024 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>121210372</v>
       </c>
       <c r="B7" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 12228-2024 artfynd.xlsx
+++ b/artfynd/A 12228-2024 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>121210372</v>
       </c>
       <c r="B7" t="n">
-        <v>90729</v>
+        <v>90730</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 12228-2024 artfynd.xlsx
+++ b/artfynd/A 12228-2024 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>121210372</v>
       </c>
       <c r="B7" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 12228-2024 artfynd.xlsx
+++ b/artfynd/A 12228-2024 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>121210372</v>
       </c>
       <c r="B7" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 12228-2024 artfynd.xlsx
+++ b/artfynd/A 12228-2024 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>121210372</v>
       </c>
       <c r="B7" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
